--- a/site/selection_finale_videos_expertise.xlsx
+++ b/site/selection_finale_videos_expertise.xlsx
@@ -521,17 +521,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Gregoire Burgé</t>
+          <t>Joël Nguyen</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>AgroParisTech</t>
+          <t>Institut d’Optique</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Innovation agro / transfert technologique</t>
+          <t>Innovation / accompagnement de projets (Institut d’Optique)</t>
         </is>
       </c>
     </row>

--- a/site/selection_finale_videos_expertise.xlsx
+++ b/site/selection_finale_videos_expertise.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -585,17 +585,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Stephanie Oger-Roussel</t>
+          <t>Fatoumata Aonon</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Communication de SATT Paris-Saclay</t>
+          <t>CNRS</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Stratégie innovation / transfert (SATT Paris-Saclay)</t>
+          <t>Valorisation recherche / accompagnement projets</t>
         </is>
       </c>
     </row>
@@ -826,214 +826,214 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>E11BIS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 12</t>
+          <t>Vidéo Expert 11 BIS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Étapes, sélection, investissement, jalons et accompagnement.</t>
+          <t>Optionnel. Regime de l'agent public (loi Allegre 1999 / loi PACTE 2019) : participer a une societe qui valorise ses travaux sans quitter l'etablissement. Temps de service, parts, fonctions. Ce n'est pas un concours de financement (i-Lab). Distinct du pacte d'associes (E17).</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon</t>
+          <t>Soizic Lefeuvre</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CNRS</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Valorisation recherche / accompagnement projets</t>
+          <t>Partenariat et valorisation / droit contrats et PI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 13</t>
+          <t>Vidéo Expert 12</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
+          <t>Étapes, sélection, investissement, jalons et accompagnement.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé</t>
+          <t>Stephanie Oger-Roussel</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>IncubAlliance</t>
+          <t>Communication de SATT Paris-Saclay</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneuriat deeptech / incubation</t>
+          <t>Stratégie innovation / transfert (SATT Paris-Saclay)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>E13BIS</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 13 BIS</t>
+          <t>Vidéo Expert 13</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Design spot, fablab, pole de competitivite, OTT, etc. — pour les start-up de nos chercheurs, pas des start-up generiques.</t>
+          <t>Coaching, réseau, formation, confrontation, équipe et préparation de la création.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Yoann Montenot</t>
+          <t>Arielle Santé</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>IncubAlliance</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Design d'innovation / Design Spot Paris-Saclay</t>
+          <t>Entrepreneuriat deeptech / incubation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E13BIS</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 14</t>
+          <t>Vidéo Expert 13 BIS</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement prive.</t>
+          <t>Design spot, fablab, pole de competitivite, OTT, etc. — pour les start-up de nos chercheurs, pas des start-up generiques.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fatoumata Aonon</t>
+          <t>Yoann Montenot</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CNRS</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Valorisation recherche / accompagnement projets</t>
+          <t>Design d'innovation / Design Spot Paris-Saclay</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 15</t>
+          <t>Vidéo Expert 14</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dilution, retour attendu, rythme de croissance, gouvernance et compatibilite avec le projet.</t>
+          <t>Prématuration, maturation, aides non dilutives, concours, Bpifrance et financement prive.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé</t>
+          <t>Fatoumata Aonon</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>IncubAlliance</t>
+          <t>CNRS</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneuriat deeptech / incubation</t>
+          <t>Valorisation recherche / accompagnement projets</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 16</t>
+          <t>Vidéo Expert 15</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et criteres humains.</t>
+          <t>Dilution, retour attendu, rythme de croissance, gouvernance et compatibilite avec le projet.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Pascal Corbel</t>
+          <t>Arielle Santé</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>IncubAlliance</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Management innovation / PI / entrepreneuriat</t>
+          <t>Entrepreneuriat deeptech / incubation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 17</t>
+          <t>Vidéo Expert 16</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Gouvernance, responsabilites, repartition du pouvoir, parts, pacte et prevention des conflits.</t>
+          <t>Complémentarité, recrutement, rôle du CEO, du CSO et du CTO, et criteres humains.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Antoine Latreille</t>
+          <t>Pascal Corbel</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1043,157 +1043,157 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Droit de l'innovation / propriété industrielle</t>
+          <t>Management innovation / PI / entrepreneuriat</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 18</t>
+          <t>Vidéo Expert 17</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Adapter le message selon l'utilisateur, le decideur, le partenaire ou l'investisseur.</t>
+          <t>Gouvernance, responsabilites, repartition du pouvoir, parts, pacte et prevention des conflits.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Arielle Santé</t>
+          <t>Antoine Latreille</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>IncubAlliance</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneuriat deeptech / incubation</t>
+          <t>Droit de l'innovation / propriété industrielle</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 19</t>
+          <t>Vidéo Expert 18</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Feedback, entrainement, mentorat et evolution de l'identite professionnelle.</t>
+          <t>Adapter le message selon l'utilisateur, le decideur, le partenaire ou l'investisseur.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Pascal Corbel</t>
+          <t>Arielle Santé</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>IncubAlliance</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Management innovation / PI / entrepreneuriat</t>
+          <t>Entrepreneuriat deeptech / incubation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 20</t>
+          <t>Vidéo Expert 19</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Double casquette, gouvernance, impartialite, evolution du metier de chercheur.</t>
+          <t>Feedback, entrainement, mentorat et evolution de l'identite professionnelle.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Bernard Yannou</t>
+          <t>Pascal Corbel</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CentraleSupélec</t>
+          <t>Université Paris-Saclay</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Innovation / design engineering / deeptech</t>
+          <t>Management innovation / PI / entrepreneuriat</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 21</t>
+          <t>Vidéo Expert 20</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
+          <t>Double casquette, gouvernance, impartialite, evolution du metier de chercheur.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Pascal Corbel</t>
+          <t>Bernard Yannou</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Université Paris-Saclay</t>
+          <t>CentraleSupélec</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Management innovation / PI / entrepreneuriat</t>
+          <t>Innovation / design engineering / deeptech</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Vidéo Expert 22</t>
+          <t>Vidéo Expert 21</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Objectifs partages, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+          <t>Incertitude, essais, erreurs, pivot et progression plutot que reussite lineaire ; leviers existants pour depasser les freins.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Rémi Waché</t>
+          <t>Pascal Corbel</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1203,37 +1203,69 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Développement de partenariats recherche-industrie</t>
+          <t>Management innovation / PI / entrepreneuriat</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Vidéo Expert 22</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Objectifs partages, complémentarité, gouvernance, engagement, création et partage de valeur.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Rémi Waché</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Université Paris-Saclay</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Développement de partenariats recherche-industrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>E23</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Vidéo Expert 23</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Confidentialite, contrats, connaissances anterieures, résultats nouveaux, PI, publication et sortie du partenariat.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Eneli Vino</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>CNRS</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Juridique PI / contrats / valorisation</t>
         </is>

--- a/site/selection_finale_videos_expertise.xlsx
+++ b/site/selection_finale_videos_expertise.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Selection finale" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection finale" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
